--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15e</t>
+          <t>15e, 16e</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>15e</t>
+          <t>15e, 16e</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>15e</t>
+          <t>15e, 16e</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>15e</t>
+          <t>15e, 16e</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>15e</t>
+          <t>15e, 16e</t>
         </is>
       </c>
     </row>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>15e</t>
+          <t>15e, 16e</t>
         </is>
       </c>
     </row>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -454,7 +454,6 @@
           <t>Doménikos</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>LE GRECO</t>
@@ -482,7 +481,6 @@
           <t>Giovanni di Niccolò de Lutero</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>DOSSO DOSSI</t>
@@ -510,7 +508,6 @@
           <t>Théophane</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>LE GREC</t>
@@ -543,7 +540,6 @@
           <t>ADAM</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>française</t>
@@ -571,7 +567,6 @@
           <t>ADAM</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>française</t>
@@ -599,7 +594,6 @@
           <t>ADAM</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>française</t>
@@ -627,7 +621,6 @@
           <t>AERTSEN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -687,7 +680,6 @@
           <t>AÏVAZOVSKI</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>russe</t>
@@ -715,7 +707,6 @@
           <t>ALGARDI</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -743,7 +734,6 @@
           <t>ALLEGRAIN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>française</t>
@@ -771,7 +761,6 @@
           <t>ALLORI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -799,7 +788,6 @@
           <t>ALMA-TADEMA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>britannique</t>
@@ -827,7 +815,6 @@
           <t>ALTDORFER</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -855,7 +842,6 @@
           <t>d'AMBROGIO</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -883,7 +869,6 @@
           <t>AMMANNATI</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -911,7 +896,6 @@
           <t>ANGUIER</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>française</t>
@@ -939,7 +923,6 @@
           <t>ANGUIER</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>française</t>
@@ -967,7 +950,6 @@
           <t>ANGUISSOLA</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -995,7 +977,6 @@
           <t>ANTOKOLSKY</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>russe</t>
@@ -1023,7 +1004,6 @@
           <t>ARCIMBOLDO</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1051,7 +1031,6 @@
           <t>ARETINO</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1079,7 +1058,6 @@
           <t>ARNOLDI</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1107,7 +1085,6 @@
           <t>ARONSON</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>russe</t>
@@ -1135,7 +1112,6 @@
           <t>ASAM</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -1163,7 +1139,6 @@
           <t>ASPETTI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1191,7 +1166,6 @@
           <t>AVERCAMP</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -1219,7 +1193,6 @@
           <t>BACHELIER</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>française</t>
@@ -1247,7 +1220,6 @@
           <t>BACON</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>Britannique</t>
@@ -1275,7 +1247,6 @@
           <t>BAKST</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>russe</t>
@@ -1303,7 +1274,6 @@
           <t>BALDOVINETTI</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1331,7 +1301,6 @@
           <t>di BALDUCCIO</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1359,7 +1328,6 @@
           <t>BALDUNG GRIEN</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -1387,7 +1355,6 @@
           <t>BALL</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -1415,7 +1382,6 @@
           <t>BANDINELLI</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1443,7 +1409,6 @@
           <t>BANDINI</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1471,7 +1436,6 @@
           <t>BANKS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>Britannique</t>
@@ -1563,7 +1527,6 @@
           <t>BARLACH</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -1591,7 +1554,6 @@
           <t>BAROCCI</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1619,7 +1581,6 @@
           <t>BARRIAS</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>française</t>
@@ -1647,7 +1608,6 @@
           <t>BARTHOLDI</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>française</t>
@@ -1675,7 +1635,6 @@
           <t>BARTOLINI</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1703,7 +1662,6 @@
           <t>di BARTOLOMEO</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1731,7 +1689,6 @@
           <t>BARYE</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>française</t>
@@ -1759,7 +1716,6 @@
           <t>BASSANO</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1787,7 +1743,6 @@
           <t>BATONI</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1815,7 +1770,6 @@
           <t>BAZILLE</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>française</t>
@@ -1875,7 +1829,6 @@
           <t>BEARDSLEY</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>britannique</t>
@@ -1903,7 +1856,6 @@
           <t>BEAUNEVEU</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>française</t>
@@ -1931,7 +1883,6 @@
           <t>BECCAFUMI</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -1959,7 +1910,6 @@
           <t>BECERRA</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -1987,7 +1937,6 @@
           <t>BECKMANN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -2015,7 +1964,6 @@
           <t>BEGAS</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -2043,7 +1991,6 @@
           <t>BELLANO</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2071,7 +2018,6 @@
           <t>BELLECHOSE</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>belge</t>
@@ -2099,7 +2045,6 @@
           <t>BELLINI</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2127,7 +2072,6 @@
           <t>BELLINI</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2155,7 +2099,6 @@
           <t>BELLOTTO</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2183,7 +2126,6 @@
           <t>BENLLIURE</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -2211,7 +2153,6 @@
           <t>BERMEJO</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -2239,7 +2180,6 @@
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>française</t>
@@ -2267,7 +2207,6 @@
           <t>BERNARD</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>française</t>
@@ -2359,7 +2298,6 @@
           <t>BERRETTINI</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2387,7 +2325,6 @@
           <t>BERRUER</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>française</t>
@@ -2415,7 +2352,6 @@
           <t>BERRUGUETE</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -2475,7 +2411,6 @@
           <t>BEUCKELAER</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>belge</t>
@@ -2503,7 +2438,6 @@
           <t>BIERSTADT</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -2531,7 +2465,6 @@
           <t>BIGARNY</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>française</t>
@@ -2559,7 +2492,6 @@
           <t>BITTER</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>autrichienne</t>
@@ -2587,7 +2519,6 @@
           <t>BLAKE</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -2615,7 +2546,6 @@
           <t>BOCCIONI</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2643,7 +2573,6 @@
           <t>BÖCKLIN</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -2671,7 +2600,6 @@
           <t>BOIZOT</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>Française</t>
@@ -2699,7 +2627,6 @@
           <t>BOLGI</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2791,7 +2718,6 @@
           <t>BONHEUR</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>française</t>
@@ -2819,7 +2745,6 @@
           <t>BONNARD</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>française</t>
@@ -2847,7 +2772,6 @@
           <t>BONTEMPS</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>française</t>
@@ -2875,7 +2799,6 @@
           <t>BORDONE</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -2903,7 +2826,6 @@
           <t>BORGLUM</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -2931,7 +2853,6 @@
           <t>BOROVIKOVSKY</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>russe</t>
@@ -2959,7 +2880,6 @@
           <t>BOSCH</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -2987,7 +2907,6 @@
           <t>BOSIO</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>française</t>
@@ -3015,7 +2934,6 @@
           <t>BOTTICELLI</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -3043,7 +2961,6 @@
           <t>BOUCHARDON</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>Française</t>
@@ -3071,7 +2988,6 @@
           <t>BOUCHER</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>française</t>
@@ -3099,7 +3015,6 @@
           <t>BOUCHER</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>française</t>
@@ -3127,7 +3042,6 @@
           <t>BOUGUEREAU</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>française</t>
@@ -3155,7 +3069,6 @@
           <t>de BOULOGNE</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>française</t>
@@ -3183,7 +3096,6 @@
           <t>BOURDELLE</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>française</t>
@@ -3211,7 +3123,6 @@
           <t>BOURDICHON</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>française</t>
@@ -3239,7 +3150,6 @@
           <t>BOUTS</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>belge</t>
@@ -3267,7 +3177,6 @@
           <t>BRACCI</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>Italienne</t>
@@ -3295,7 +3204,6 @@
           <t>BRAUN</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>tchèque</t>
@@ -3323,7 +3231,6 @@
           <t>BREGNO</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -3351,7 +3258,6 @@
           <t>BRIDAN</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>Française</t>
@@ -3379,7 +3285,6 @@
           <t>BROEDERLAM</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>belge</t>
@@ -3407,7 +3312,6 @@
           <t>BRONZINO</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -3435,7 +3339,6 @@
           <t>BROUWER</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>belge</t>
@@ -3463,7 +3366,6 @@
           <t>BRUEGEL L'ANCIEN</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>belge</t>
@@ -3491,7 +3393,6 @@
           <t>BRÜGGEMANN</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -3519,7 +3420,6 @@
           <t>LE BRUN</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>française</t>
@@ -3547,7 +3447,6 @@
           <t>BUGATTI</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -3639,7 +3538,6 @@
           <t>BURNE-JONES</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -3667,7 +3565,6 @@
           <t>BUSHNELL</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -3695,7 +3592,6 @@
           <t>BUSTELLI</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -3723,7 +3619,6 @@
           <t>CABANEL</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>française</t>
@@ -3751,7 +3646,6 @@
           <t>CAFFÀ</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>maltaise</t>
@@ -3779,7 +3673,6 @@
           <t>CAFFIERI</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>française</t>
@@ -3807,7 +3700,6 @@
           <t>CAILLEBOTTE</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>française</t>
@@ -3835,7 +3727,6 @@
           <t>CALDER</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -3863,7 +3754,6 @@
           <t>di CAMAINO</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -3891,7 +3781,6 @@
           <t>CAMPAGNA</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -3919,7 +3808,6 @@
           <t>da CAMPIONE</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -3979,7 +3867,6 @@
           <t>CANO</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -4007,7 +3894,6 @@
           <t>CANOVA</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>Italienne</t>
@@ -4035,7 +3921,6 @@
           <t>CARMONA</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -4063,7 +3948,6 @@
           <t>CARPACCIO</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4091,7 +3975,6 @@
           <t>CARPEAUX</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>française</t>
@@ -4151,7 +4034,6 @@
           <t>CARRIER-BELLEUSE</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>française</t>
@@ -4179,7 +4061,6 @@
           <t>CARRIERA</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4207,7 +4088,6 @@
           <t>CASSATT</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -4235,7 +4115,6 @@
           <t>del CASTAGNO</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4263,7 +4142,6 @@
           <t>CATTANEO</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4291,7 +4169,6 @@
           <t>CAVALLINI</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4319,7 +4196,6 @@
           <t>CELLINI</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4347,7 +4223,6 @@
           <t>CÉZANNE</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>française</t>
@@ -4375,7 +4250,6 @@
           <t>de CHAMPAIGNE</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>française</t>
@@ -4403,7 +4277,6 @@
           <t>CHANTREY</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -4431,7 +4304,6 @@
           <t>CHAPU</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>française</t>
@@ -4459,7 +4331,6 @@
           <t>CHARDIN</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>française</t>
@@ -4487,7 +4358,6 @@
           <t>CHASSÉRIAU</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>française</t>
@@ -4515,7 +4385,6 @@
           <t>CHEN</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -4543,7 +4412,6 @@
           <t>CHINARD</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>française</t>
@@ -4571,7 +4439,6 @@
           <t>CHRISTOPHE</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>française</t>
@@ -4599,7 +4466,6 @@
           <t>CHRISTUS</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>belge</t>
@@ -4627,7 +4493,6 @@
           <t>CHURCH</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -4655,7 +4520,6 @@
           <t>CIBBER</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>danoise</t>
@@ -4673,13 +4537,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
           <t>CIMABUE</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4739,7 +4601,6 @@
           <t>di CIONE</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4767,7 +4628,6 @@
           <t>CIVITALI</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -4795,7 +4655,6 @@
           <t>CLAESZ</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -4823,7 +4682,6 @@
           <t>CLAESZOON HEDA</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -4851,7 +4709,6 @@
           <t>CLAUDEL</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>française</t>
@@ -4879,7 +4736,6 @@
           <t>CLÉSINGER</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>française</t>
@@ -4907,7 +4763,6 @@
           <t>CLOUET</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>française</t>
@@ -4935,7 +4790,6 @@
           <t>CLOUET</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>française</t>
@@ -4963,7 +4817,6 @@
           <t>COLE</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -4991,7 +4844,6 @@
           <t>COLLOT</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>française</t>
@@ -5019,7 +4871,6 @@
           <t>COLOMBE</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>française</t>
@@ -5047,7 +4898,6 @@
           <t>COLOMBE</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>française</t>
@@ -5075,7 +4925,6 @@
           <t>van CONINXLOO</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>belge</t>
@@ -5103,7 +4952,6 @@
           <t>CONSTABLE</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -5131,7 +4979,6 @@
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -5159,7 +5006,6 @@
           <t>CORDIER</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>française</t>
@@ -5187,7 +5033,6 @@
           <t>CORDIER</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>française</t>
@@ -5215,7 +5060,6 @@
           <t>CORINTH</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -5243,7 +5087,6 @@
           <t>CORNACCHINI</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -5271,7 +5114,6 @@
           <t>COROT</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>française</t>
@@ -5299,7 +5141,6 @@
           <t>CORRADINI</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -5359,7 +5200,6 @@
           <t>di COSIMO</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -5387,7 +5227,6 @@
           <t>del COSSA</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -5415,7 +5254,6 @@
           <t>COURBET</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>française</t>
@@ -5443,7 +5281,6 @@
           <t>LE COURT</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -5471,7 +5308,6 @@
           <t>COUSIN L'ANCIEN</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>française</t>
@@ -5499,7 +5335,6 @@
           <t>COUSTOU</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>française</t>
@@ -5527,7 +5362,6 @@
           <t>COUSTOU L'Ancien</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>Française</t>
@@ -5555,7 +5389,6 @@
           <t>COUSTOU Le Jeune</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>française</t>
@@ -5583,7 +5416,6 @@
           <t>COYSEVOX</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>française</t>
@@ -5611,7 +5443,6 @@
           <t>CRANACH L'ANCIEN</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -5639,7 +5470,6 @@
           <t>CRANACH le JEUNE</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -5667,7 +5497,6 @@
           <t>CRAUK</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>française</t>
@@ -5695,7 +5524,6 @@
           <t>CRIVELLI</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -5723,7 +5551,6 @@
           <t>CUYP</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -5751,7 +5578,6 @@
           <t>DADDI</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -5779,7 +5605,6 @@
           <t>DALLIN</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -5807,7 +5632,6 @@
           <t>DALOU</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>française</t>
@@ -5835,7 +5659,6 @@
           <t>DANTI</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -5863,7 +5686,6 @@
           <t>DAUCHER</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -5891,7 +5713,6 @@
           <t>DAUMIER</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>française</t>
@@ -5919,7 +5740,6 @@
           <t>DAVID</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>belge</t>
@@ -5947,7 +5767,6 @@
           <t>DAVID</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>française</t>
@@ -6007,7 +5826,6 @@
           <t>DEGAS</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>française</t>
@@ -6035,7 +5853,6 @@
           <t>DELACROIX</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>française</t>
@@ -6063,7 +5880,6 @@
           <t>DELAUNAY</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>française</t>
@@ -6091,7 +5907,6 @@
           <t>dell'ARCA</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -6119,7 +5934,6 @@
           <t>DELVAUX</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>Belge</t>
@@ -6147,7 +5961,6 @@
           <t>DENIS</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>française</t>
@@ -6175,7 +5988,6 @@
           <t>van der GOES</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6203,7 +6015,6 @@
           <t>van der SCHARDT</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -6231,7 +6042,6 @@
           <t>VAN DER VOORT LE VIEUX</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>Flamande</t>
@@ -6259,7 +6069,6 @@
           <t>van der WEYDEN</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6287,7 +6096,6 @@
           <t>DERAIN</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>française</t>
@@ -6315,7 +6123,6 @@
           <t>DESJARDINS</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>française</t>
@@ -6343,7 +6150,6 @@
           <t>DESPIAU</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>française</t>
@@ -6371,7 +6177,6 @@
           <t>van DOESBURG</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -6399,7 +6204,6 @@
           <t>DONNER</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>Autrichienne</t>
@@ -6427,7 +6231,6 @@
           <t>DORÉ</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>française</t>
@@ -6455,7 +6258,6 @@
           <t>DOU</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -6483,7 +6285,6 @@
           <t>DOVE</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -6511,7 +6312,6 @@
           <t>DREYER</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -6539,7 +6339,6 @@
           <t>DROUAIS</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>française</t>
@@ -6567,7 +6366,6 @@
           <t>DUBOIS</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>française</t>
@@ -6595,7 +6393,6 @@
           <t>DUBROEUCQ</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6623,7 +6420,6 @@
           <t>di DUCCIO</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -6651,7 +6447,6 @@
           <t>DUCREUX</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
           <t>française</t>
@@ -6679,7 +6474,6 @@
           <t>DUFY</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>française</t>
@@ -6707,7 +6501,6 @@
           <t>DUPRÉ</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -6735,7 +6528,6 @@
           <t>DUQUESNOY</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6763,7 +6555,6 @@
           <t>DUQUESNOY LE JEUNE</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6791,7 +6582,6 @@
           <t>DURER</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -6819,7 +6609,6 @@
           <t>van DYCK</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6847,7 +6636,6 @@
           <t>EAKINS</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -6875,7 +6663,6 @@
           <t>EGELL</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -6903,7 +6690,6 @@
           <t>EGGERS</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6931,7 +6717,6 @@
           <t>ENSOR</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>belge</t>
@@ -6959,7 +6744,6 @@
           <t>ETEX</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
           <t>française</t>
@@ -6987,7 +6771,6 @@
           <t>EWORTH</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>belge</t>
@@ -7015,7 +6798,6 @@
           <t>d'EYCK</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>belge</t>
@@ -7043,7 +6825,6 @@
           <t>van EYCK</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>belge</t>
@@ -7071,7 +6852,6 @@
           <t>FABRE</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>française</t>
@@ -7099,7 +6879,6 @@
           <t>da FABRIANO</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7127,7 +6906,6 @@
           <t>FABRITIUS</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -7155,7 +6933,6 @@
           <t>FALCONET</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>Française</t>
@@ -7183,7 +6960,6 @@
           <t>FALGUIÈRE</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>française</t>
@@ -7211,7 +6987,6 @@
           <t>FANCELLI</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7239,7 +7014,6 @@
           <t>FANCELLI</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7267,7 +7041,6 @@
           <t>FANZAGO</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7295,7 +7068,6 @@
           <t>FATTORI</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7323,7 +7095,6 @@
           <t>FAYDHERBE</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>belge</t>
@@ -7351,7 +7122,6 @@
           <t>FEDI</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7379,7 +7149,6 @@
           <t>FERNÁNDEZ</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -7407,7 +7176,6 @@
           <t>FERRATA</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7435,7 +7203,6 @@
           <t>FEUCHTMAYER</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>Allemande</t>
@@ -7463,7 +7230,6 @@
           <t>da FIESOLE</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7491,7 +7257,6 @@
           <t>FILLA</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>tchèque</t>
@@ -7519,7 +7284,6 @@
           <t>FILONOV</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>russe</t>
@@ -7547,7 +7311,6 @@
           <t>FINELLI</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7575,7 +7338,6 @@
           <t>da FIRENZE</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7603,7 +7365,6 @@
           <t>de FLANDES</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -7631,7 +7392,6 @@
           <t>FLAXMAN</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -7659,7 +7419,6 @@
           <t>FLORIS</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>belge</t>
@@ -7687,7 +7446,6 @@
           <t>FLORIS</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>belge</t>
@@ -7715,7 +7473,6 @@
           <t>FLÖTNER</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -7743,7 +7500,6 @@
           <t>FOGGINI</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7771,7 +7527,6 @@
           <t>FONTANA</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7799,7 +7554,6 @@
           <t>FOPPA</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7827,7 +7581,6 @@
           <t>da FORLÌ</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7855,7 +7608,6 @@
           <t>FORMENT</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -7883,7 +7635,6 @@
           <t>FOUCOU</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>Française</t>
@@ -7911,7 +7662,6 @@
           <t>FOUQUET</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>française</t>
@@ -7939,7 +7689,6 @@
           <t>FRAGONARD</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>française</t>
@@ -7967,7 +7716,6 @@
           <t>della FRANCESCA</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -7995,7 +7743,6 @@
           <t>di FRANCESCO</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8023,7 +7770,6 @@
           <t>FRÉMIET</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>française</t>
@@ -8051,7 +7797,6 @@
           <t>FRENCH</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -8079,7 +7824,6 @@
           <t>FRIEDRICH</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -8107,7 +7851,6 @@
           <t>FRIESZ</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>française</t>
@@ -8135,7 +7878,6 @@
           <t>FUSELI</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -8163,7 +7905,6 @@
           <t>GADDI</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8191,7 +7932,6 @@
           <t>GAGINI</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8219,7 +7959,6 @@
           <t>GAINSBOROUGH</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -8247,7 +7986,6 @@
           <t>GALLEGO</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -8275,7 +8013,6 @@
           <t>GAUGUIN</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>française</t>
@@ -8303,7 +8040,6 @@
           <t>GEEFS</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>belge</t>
@@ -8363,7 +8099,6 @@
           <t>GEMITO</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8391,7 +8126,6 @@
           <t>GENTILESCHI</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8419,7 +8153,6 @@
           <t>GENTILESCHI</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8447,7 +8180,6 @@
           <t>GERHAERT van LEYDEN</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -8475,7 +8207,6 @@
           <t>GERHARD</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -8503,7 +8234,6 @@
           <t>GÉRICAULT</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>française</t>
@@ -8531,7 +8261,6 @@
           <t>GÉRÔME</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>française</t>
@@ -8559,7 +8288,6 @@
           <t>GHEERAERTS le JEUNE</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>belge</t>
@@ -8587,7 +8315,6 @@
           <t>GHIBERTI</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8615,7 +8342,6 @@
           <t>GHIRLANDAIO</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8643,7 +8369,6 @@
           <t>GIBBONS</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
           <t>Néerladais</t>
@@ -8671,7 +8396,6 @@
           <t>GIBSON</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -8699,7 +8423,6 @@
           <t>GILBERT</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -8727,7 +8450,6 @@
           <t>GILL</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -8755,7 +8477,6 @@
           <t>GIORDANO</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8783,7 +8504,6 @@
           <t>di GIORGIO MARTINI</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8811,7 +8531,6 @@
           <t>di GIOVANNI</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8839,7 +8558,6 @@
           <t>di GIOVANNI</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -8931,7 +8649,6 @@
           <t>GIRARDON</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>française</t>
@@ -8959,7 +8676,6 @@
           <t>GIRODET</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>française</t>
@@ -8987,7 +8703,6 @@
           <t>GODEBSKI</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>polonaise</t>
@@ -9015,7 +8730,6 @@
           <t>GODECHARLE</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>Belge</t>
@@ -9043,7 +8757,6 @@
           <t>van GOGH</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -9071,7 +8784,6 @@
           <t>GONÇALVES</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>portugaise</t>
@@ -9099,7 +8811,6 @@
           <t>GONZÁLEZ</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -9159,7 +8870,6 @@
           <t>GOUJON</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
           <t>française</t>
@@ -9187,7 +8897,6 @@
           <t>de GOYA</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -9215,7 +8924,6 @@
           <t>van GOYEN</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -9243,7 +8951,6 @@
           <t>GOZZOLI</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -9271,7 +8978,6 @@
           <t>GRAFF</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -9299,7 +9005,6 @@
           <t>GREUZE</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
           <t>française</t>
@@ -9327,7 +9032,6 @@
           <t>GRIGORIEV</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>russe</t>
@@ -9355,7 +9059,6 @@
           <t>GRÜNEWALD</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -9383,7 +9086,6 @@
           <t>GUARDI</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -9411,7 +9113,6 @@
           <t>GUIBAL</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>française</t>
@@ -9439,7 +9140,6 @@
           <t>GUIDI</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -9467,7 +9167,6 @@
           <t>GUILLAIN</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>française</t>
@@ -9495,7 +9194,6 @@
           <t>GÜNTHER</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>Allemande</t>
@@ -9523,7 +9221,6 @@
           <t>GÜNTHER</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>Allemande</t>
@@ -9551,7 +9248,6 @@
           <t>HALS</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -9579,7 +9275,6 @@
           <t>HARTLEY</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -9607,7 +9302,6 @@
           <t>HAYEZ</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -9635,7 +9329,6 @@
           <t>van HEEMSKERCK</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -9663,7 +9356,6 @@
           <t>van HEMESSEN</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>belge</t>
@@ -9691,7 +9383,6 @@
           <t>van HEMESSEN</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>belge</t>
@@ -9719,7 +9410,6 @@
           <t>HENNER</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>française</t>
@@ -9747,7 +9437,6 @@
           <t>HERING</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -9775,7 +9464,6 @@
           <t>HERNÁNDEZ</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -9803,7 +9491,6 @@
           <t>von HILDEBRAND</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -9831,7 +9518,6 @@
           <t>HILLIARD</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -9859,7 +9545,6 @@
           <t>HISHIKAWA</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
           <t>japonaise</t>
@@ -9887,7 +9572,6 @@
           <t>HOBBEMA</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -9915,7 +9599,6 @@
           <t>HODLER</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -9943,7 +9626,6 @@
           <t>HOGARTH</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -9971,7 +9653,6 @@
           <t>HOKUSAI</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>japonaise</t>
@@ -9999,7 +9680,6 @@
           <t>HOLBEIN le JEUNE</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -10027,7 +9707,6 @@
           <t>HOMER</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -10055,7 +9734,6 @@
           <t>LE HONGRE</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>française</t>
@@ -10083,7 +9761,6 @@
           <t>van HONTHORST</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -10111,7 +9788,6 @@
           <t>de HOOCH</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -10139,7 +9815,6 @@
           <t>HORENBOUT</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>belge</t>
@@ -10167,7 +9842,6 @@
           <t>HOSMER</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -10195,7 +9869,6 @@
           <t>HOUDON</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
           <t>Française</t>
@@ -10223,7 +9896,6 @@
           <t>HUA</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -10251,7 +9923,6 @@
           <t>HUANG</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -10279,7 +9950,6 @@
           <t>HUGUET</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -10307,7 +9977,6 @@
           <t>INGRES</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>française</t>
@@ -10335,7 +10004,6 @@
           <t>INJALBERT</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>française</t>
@@ -10363,7 +10031,6 @@
           <t>ITŌ</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
           <t>japonaise</t>
@@ -10423,7 +10090,6 @@
           <t>JACQUIOT</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>française</t>
@@ -10451,7 +10117,6 @@
           <t>JAMETE</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>française</t>
@@ -10479,7 +10144,6 @@
           <t>JAMNITZER</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -10507,7 +10171,6 @@
           <t>von JAWLENSKY</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>russe</t>
@@ -10535,7 +10198,6 @@
           <t>JOHN</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -10563,7 +10225,6 @@
           <t>JONGKIND</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -10591,7 +10252,6 @@
           <t>JORDAENS</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>belge</t>
@@ -10609,13 +10269,11 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
           <t>JUAN GRIS</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -10643,7 +10301,6 @@
           <t>JULIEN</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>Française</t>
@@ -10671,7 +10328,6 @@
           <t>de JUNI</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>française</t>
@@ -10699,7 +10355,6 @@
           <t>JUSTE</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -10727,7 +10382,6 @@
           <t>JUVARRA</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>Italienne</t>
@@ -10755,7 +10409,6 @@
           <t>KAHLO</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>mexicaine</t>
@@ -10783,7 +10436,6 @@
           <t>KALF</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -10811,7 +10463,6 @@
           <t>KANDINSKY</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
           <t>russe</t>
@@ -10839,7 +10490,6 @@
           <t>KÄNDLER</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>Allemande</t>
@@ -10867,7 +10517,6 @@
           <t>KANŌ</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
           <t>japonaise</t>
@@ -10895,7 +10544,6 @@
           <t>KAUFFMAN</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -10923,7 +10571,6 @@
           <t>DE KEYSER</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -10951,7 +10598,6 @@
           <t>KIRCHNER</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -10979,7 +10625,6 @@
           <t>KISLING</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>polonaise</t>
@@ -11007,7 +10652,6 @@
           <t>KLEE</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -11035,7 +10679,6 @@
           <t>KLIMT</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>autrichienne</t>
@@ -11063,7 +10706,6 @@
           <t>af KLINT</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>suédoise</t>
@@ -11091,7 +10733,6 @@
           <t>KLODT</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
           <t>russe</t>
@@ -11119,7 +10760,6 @@
           <t>KOLBE</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -11147,7 +10787,6 @@
           <t>KOLLWITZ</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -11175,7 +10814,6 @@
           <t>KRAFT</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -11203,7 +10841,6 @@
           <t>KRUMPPER</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -11231,7 +10868,6 @@
           <t>KUBIŠTA</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>tchèque</t>
@@ -11259,7 +10895,6 @@
           <t>LABILLE-GUIARD</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>française</t>
@@ -11287,7 +10922,6 @@
           <t>LADD</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -11315,7 +10949,6 @@
           <t>LAMBEAUX</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
           <t>belge</t>
@@ -11343,7 +10976,6 @@
           <t>LANCRET</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
           <t>française</t>
@@ -11371,7 +11003,6 @@
           <t>LANDINI</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -11389,7 +11020,6 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
           <t>LANG SHINING</t>
@@ -11427,7 +11057,6 @@
           <t>de LARGILLIÈRE</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
           <t>française</t>
@@ -11455,7 +11084,6 @@
           <t>LAURANA</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -11483,7 +11111,6 @@
           <t>LAWRENCE</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -11511,7 +11138,6 @@
           <t>LÉGER</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
           <t>française</t>
@@ -11539,7 +11165,6 @@
           <t>LEGROS L'AÎNÉ</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
           <t>française</t>
@@ -11567,7 +11192,6 @@
           <t>LEGROS LE JEUNE</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
           <t>française</t>
@@ -11595,7 +11219,6 @@
           <t>LEHMBRUCK</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -11623,7 +11246,6 @@
           <t>LEIGHTON</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -11651,7 +11273,6 @@
           <t>LEINBERGER</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -11679,7 +11300,6 @@
           <t>LELY</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -11707,7 +11327,6 @@
           <t>LEMOYNE</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
           <t>française</t>
@@ -11735,7 +11354,6 @@
           <t>LEONI</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -11763,7 +11381,6 @@
           <t>LEONI</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -11791,7 +11408,6 @@
           <t>LEOPARDI</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -11819,7 +11435,6 @@
           <t>LEVITZKY</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
           <t>russe</t>
@@ -11847,7 +11462,6 @@
           <t>LEWIS</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -11875,7 +11489,6 @@
           <t>van LEYDEN</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -11903,7 +11516,6 @@
           <t>LEYSTER</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -11931,7 +11543,6 @@
           <t>de LIÈGE</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
           <t>française</t>
@@ -11959,7 +11570,6 @@
           <t>LIEVENS</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -11987,7 +11597,6 @@
           <t>LIOTARD</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
           <t>française</t>
@@ -12015,7 +11624,6 @@
           <t>LIPPI</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12043,7 +11651,6 @@
           <t>LIPPI</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12071,7 +11678,6 @@
           <t>LOCHNER</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -12099,7 +11705,6 @@
           <t>LOMBARDO</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12127,7 +11732,6 @@
           <t>LONGHI</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12155,7 +11759,6 @@
           <t>van LOO</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
           <t>française</t>
@@ -12183,7 +11786,6 @@
           <t>LORENZETTI</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12211,7 +11813,6 @@
           <t>LORENZETTI</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12239,7 +11840,6 @@
           <t>LE LORRAIN</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
           <t>française</t>
@@ -12267,7 +11867,6 @@
           <t>LOTTO</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12295,7 +11894,6 @@
           <t>LUINI</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12323,7 +11921,6 @@
           <t>MACKE</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -12351,7 +11948,6 @@
           <t>MADERNO</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12379,7 +11975,6 @@
           <t>MAES</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -12407,7 +12002,6 @@
           <t>MAGNASCO</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12435,7 +12029,6 @@
           <t>da MAIANO</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12463,7 +12056,6 @@
           <t>MAILLOL</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
           <t>française</t>
@@ -12491,7 +12083,6 @@
           <t>MAINI</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12519,7 +12110,6 @@
           <t>MAITANI</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12537,13 +12127,11 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
           <t>MAÎTRE DU DIPTYQUE DE WILTON</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -12571,7 +12159,6 @@
           <t>MALEVICH</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
           <t>russe</t>
@@ -12599,7 +12186,6 @@
           <t>MANET</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
           <t>française</t>
@@ -12627,7 +12213,6 @@
           <t>MANGUIN</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
           <t>française</t>
@@ -12655,7 +12240,6 @@
           <t>MANTEGNA</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12683,7 +12267,6 @@
           <t>MARC</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -12711,7 +12294,6 @@
           <t>MARIANI</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12739,7 +12321,6 @@
           <t>MARMION</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
           <t>française</t>
@@ -12767,7 +12348,6 @@
           <t>MARQUET</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
           <t>française</t>
@@ -12795,7 +12375,6 @@
           <t>DE MARSY</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -12823,7 +12402,6 @@
           <t>MARSY</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>française</t>
@@ -12851,7 +12429,6 @@
           <t>MARTÍNEZ MONTAÑÉS</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -12879,7 +12456,6 @@
           <t>MARTINI</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -12907,7 +12483,6 @@
           <t>MARUYAMA</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
           <t>japonaise</t>
@@ -12935,7 +12510,6 @@
           <t>MATISSE</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>française</t>
@@ -12995,7 +12569,6 @@
           <t>MAZZONI</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13023,7 +12596,6 @@
           <t>MEIT</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -13051,7 +12623,6 @@
           <t>MELÉNDEZ</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -13079,7 +12650,6 @@
           <t>MEMLING</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
           <t>belge</t>
@@ -13107,7 +12677,6 @@
           <t>MEMMI</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13135,7 +12704,6 @@
           <t>DE MENA</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -13163,7 +12731,6 @@
           <t>de' MENABUOI</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13191,7 +12758,6 @@
           <t>MENGS</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -13219,7 +12785,6 @@
           <t>MERCIÉ</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
           <t>française</t>
@@ -13279,7 +12844,6 @@
           <t>MESSERSCHMIDT</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
           <t>autrichienne</t>
@@ -13307,7 +12871,6 @@
           <t>da MESSINA</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13335,7 +12898,6 @@
           <t>METSU</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -13363,7 +12925,6 @@
           <t>METSYS</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
           <t>belge</t>
@@ -13391,7 +12952,6 @@
           <t>MEUNIER</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
           <t>belge</t>
@@ -13451,7 +13011,6 @@
           <t>MILLAIS</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -13479,7 +13038,6 @@
           <t>MILLET</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
           <t>française</t>
@@ -13507,7 +13065,6 @@
           <t>MILLET</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
           <t>française</t>
@@ -13535,7 +13092,6 @@
           <t>MOCHI</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13563,7 +13119,6 @@
           <t>da MODENA</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13591,7 +13146,6 @@
           <t>MODIGLIANI</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13619,7 +13173,6 @@
           <t>MOHOLY-NAGY</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>hongroise</t>
@@ -13647,7 +13200,6 @@
           <t>MOITTE</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
           <t>française</t>
@@ -13675,7 +13227,6 @@
           <t>MOLL</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>Autrichienne</t>
@@ -13703,7 +13254,6 @@
           <t>MONACO</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13731,7 +13281,6 @@
           <t>MONDRIAN</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -13759,7 +13308,6 @@
           <t>MONE</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
           <t>belge</t>
@@ -13787,7 +13335,6 @@
           <t>MONET</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
           <t>française</t>
@@ -13815,7 +13362,6 @@
           <t>MOR</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -13843,7 +13389,6 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -13871,7 +13416,6 @@
           <t>DE MORA</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -13899,7 +13443,6 @@
           <t>de MORALES</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -13927,7 +13470,6 @@
           <t>MOREAU</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
           <t>française</t>
@@ -13955,7 +13497,6 @@
           <t>MOREAU</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
           <t>française</t>
@@ -13983,7 +13524,6 @@
           <t>MORISOT</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
           <t>française</t>
@@ -14011,7 +13551,6 @@
           <t>MORLAITER</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -14039,7 +13578,6 @@
           <t>MORONI</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -14067,7 +13605,6 @@
           <t>MUCHA</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
         <is>
           <t>tchèque</t>
@@ -14095,7 +13632,6 @@
           <t>MUELLER</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -14123,7 +13659,6 @@
           <t>MUKHINA</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr">
         <is>
           <t>russe</t>
@@ -14151,7 +13686,6 @@
           <t>MUNCH</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
           <t>norvégienne</t>
@@ -14179,7 +13713,6 @@
           <t>MURILLO</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -14207,7 +13740,6 @@
           <t>MUSA</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr">
         <is>
           <t>persane</t>
@@ -14235,7 +13767,6 @@
           <t>MYSLBEK</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
           <t>tchèque</t>
@@ -14263,7 +13794,6 @@
           <t>NACCHERINO</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -14291,7 +13821,6 @@
           <t>NAHL</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -14319,7 +13848,6 @@
           <t>LE NAIN</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
           <t>française</t>
@@ -14347,7 +13875,6 @@
           <t>NASH</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -14375,7 +13902,6 @@
           <t>NATOIRE</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr">
         <is>
           <t>française</t>
@@ -14403,7 +13929,6 @@
           <t>NATTIER</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr">
         <is>
           <t>française</t>
@@ -14463,7 +13988,6 @@
           <t>NEVINSON</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -14491,7 +14015,6 @@
           <t>NI</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -14551,7 +14074,6 @@
           <t>NOLLEKENS</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -14579,7 +14101,6 @@
           <t>NOSSENI</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -14607,7 +14128,6 @@
           <t>ORDÓÑEZ</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -14635,7 +14155,6 @@
           <t>van OSTADE</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -14663,7 +14182,6 @@
           <t>OUDRY</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
         <is>
           <t>française</t>
@@ -14691,7 +14209,6 @@
           <t>PACHER</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr">
         <is>
           <t>autrichienne</t>
@@ -14719,7 +14236,6 @@
           <t>PAJOU</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr">
         <is>
           <t>Française</t>
@@ -14747,7 +14263,6 @@
           <t>PANTOJA de la Cruz</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -14775,7 +14290,6 @@
           <t>PARLER</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -14803,7 +14317,6 @@
           <t>PARODI</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -14831,7 +14344,6 @@
           <t>PASCIN</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr">
         <is>
           <t>bulgare</t>
@@ -14859,7 +14371,6 @@
           <t>PATINIR</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
       <c r="D513" t="inlineStr">
         <is>
           <t>belge</t>
@@ -14887,7 +14398,6 @@
           <t>PEALE</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -14915,7 +14425,6 @@
           <t>PÉPIN de HUY</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr">
         <is>
           <t>française</t>
@@ -14943,7 +14452,6 @@
           <t>PERMOSER</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -14971,7 +14479,6 @@
           <t>PERRAUD</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
           <t>française</t>
@@ -14999,7 +14506,6 @@
           <t>PERRONNEAU</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr">
         <is>
           <t>française</t>
@@ -15059,7 +14565,6 @@
           <t>PETEL</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -15087,7 +14592,6 @@
           <t>PICABIA</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
         <is>
           <t>française</t>
@@ -15179,7 +14683,6 @@
           <t>PIGALLE</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr"/>
       <c r="D524" t="inlineStr">
         <is>
           <t>Française</t>
@@ -15207,7 +14710,6 @@
           <t>PILON</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr"/>
       <c r="D525" t="inlineStr">
         <is>
           <t>française</t>
@@ -15235,7 +14737,6 @@
           <t>del PIOMBO</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15263,7 +14764,6 @@
           <t>PIQUER Y DUART</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -15291,7 +14791,6 @@
           <t>PISANO</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15319,7 +14818,6 @@
           <t>PISANO</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15347,7 +14845,6 @@
           <t>PISANO</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15375,7 +14872,6 @@
           <t>PISSARRO</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr">
         <is>
           <t>française</t>
@@ -15403,7 +14899,6 @@
           <t>del POLLAIOLO</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15431,7 +14926,6 @@
           <t>POLLAIUOLO</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15459,7 +14953,6 @@
           <t>POMPON</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr">
         <is>
           <t>française</t>
@@ -15487,7 +14980,6 @@
           <t>PONTORMO</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15515,7 +15007,6 @@
           <t>della PORTA</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15543,7 +15034,6 @@
           <t>della PORTA</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15571,7 +15061,6 @@
           <t>POSADA</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
           <t>mexicaine</t>
@@ -15599,7 +15088,6 @@
           <t>POUSSIN</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
           <t>française</t>
@@ -15627,7 +15115,6 @@
           <t>POWERS</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -15655,7 +15142,6 @@
           <t>POYER</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr">
         <is>
           <t>française</t>
@@ -15683,7 +15169,6 @@
           <t>PRADIER</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -15711,7 +15196,6 @@
           <t>PRATT</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -15739,7 +15223,6 @@
           <t>PRÉAULT</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr">
         <is>
           <t>française</t>
@@ -15767,7 +15250,6 @@
           <t>PRETI</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15795,7 +15277,6 @@
           <t>PRIEUR</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
           <t>française</t>
@@ -15823,7 +15304,6 @@
           <t>PRIMATICCIO</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -15851,7 +15331,6 @@
           <t>PUCELLE</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
           <t>française</t>
@@ -15879,7 +15358,6 @@
           <t>PUGET</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
           <t>française</t>
@@ -15907,7 +15385,6 @@
           <t>PUVIS de CHAVANNES</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr">
         <is>
           <t>française</t>
@@ -15935,7 +15412,6 @@
           <t>QUARTON</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
           <t>française</t>
@@ -15963,7 +15439,6 @@
           <t>QUEIROLO</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
           <t>Italienne</t>
@@ -15991,7 +15466,6 @@
           <t>QUELLINUS III</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
           <t>Flamande</t>
@@ -16019,7 +15493,6 @@
           <t>QUELLINUS L'ANCIEN</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
         <is>
           <t>belge</t>
@@ -16047,7 +15520,6 @@
           <t>della QUERCIA</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16075,7 +15547,6 @@
           <t>RAEBURN</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr">
         <is>
           <t>écossaise (Royaume-Uni)</t>
@@ -16103,7 +15574,6 @@
           <t>RAGGI</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16131,7 +15601,6 @@
           <t>RAMSAY</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -16159,7 +15628,6 @@
           <t>RAUCH</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -16187,7 +15655,6 @@
           <t>RAUCHMILLER</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -16215,7 +15682,6 @@
           <t>REDON</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr">
         <is>
           <t>française</t>
@@ -16243,7 +15709,6 @@
           <t>REGNAUDIN</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr">
         <is>
           <t>française</t>
@@ -16271,7 +15736,6 @@
           <t>REICHLE</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -16299,7 +15763,6 @@
           <t>REMINGTON</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -16327,7 +15790,6 @@
           <t>RENI</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16355,7 +15817,6 @@
           <t>RENOIR</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr">
         <is>
           <t>française</t>
@@ -16383,7 +15844,6 @@
           <t>REPINE</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
           <t>russe</t>
@@ -16411,7 +15871,6 @@
           <t>REYNOLDS</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -16439,7 +15898,6 @@
           <t>de RIBERA</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -16467,7 +15925,6 @@
           <t>RICHIER</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
           <t>française</t>
@@ -16495,7 +15952,6 @@
           <t>RIEMENSCHNEIDER</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -16523,7 +15979,6 @@
           <t>RIETSCHEL</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -16551,7 +16006,6 @@
           <t>RIGAUD</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr">
         <is>
           <t>française</t>
@@ -16611,7 +16065,6 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16639,7 +16092,6 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16667,7 +16119,6 @@
           <t>ROBERT</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
           <t>française</t>
@@ -16695,7 +16146,6 @@
           <t>de' ROBERTI</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16755,7 +16205,6 @@
           <t>RODIN</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr">
         <is>
           <t>française</t>
@@ -16783,7 +16232,6 @@
           <t>ROERICH</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr">
         <is>
           <t>russe</t>
@@ -16811,7 +16259,6 @@
           <t>ROGERS</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -16839,7 +16286,6 @@
           <t>ROKOTOV</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr">
         <is>
           <t>russe</t>
@@ -16899,7 +16345,6 @@
           <t>ROLDÁN</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -16927,7 +16372,6 @@
           <t>ROMANO</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr"/>
       <c r="D586" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16955,7 +16399,6 @@
           <t>ROSA</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -16983,7 +16426,6 @@
           <t>ROSLIN</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr">
         <is>
           <t>suédoise</t>
@@ -17011,7 +16453,6 @@
           <t>ROSSELLI</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17039,7 +16480,6 @@
           <t>ROSSELLINO</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17067,7 +16507,6 @@
           <t>ROSSELLINO</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17095,7 +16534,6 @@
           <t>ROSSETTI</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -17123,7 +16561,6 @@
           <t>de' ROSSI</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17151,7 +16588,6 @@
           <t>ROUBILIAC</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
           <t>Française</t>
@@ -17211,7 +16647,6 @@
           <t>ROUSSEAU</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
           <t>française</t>
@@ -17239,7 +16674,6 @@
           <t>ROUSSEL</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
           <t>française</t>
@@ -17267,7 +16701,6 @@
           <t>RUBENS</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
           <t>belge</t>
@@ -17295,7 +16728,6 @@
           <t>RUDE</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
           <t>française</t>
@@ -17323,7 +16755,6 @@
           <t>van RUISDAEL</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -17351,7 +16782,6 @@
           <t>RUSCONI</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17379,7 +16809,6 @@
           <t>van RUYSDAEL</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -17407,7 +16836,6 @@
           <t>RYSBRACK</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
           <t>belge</t>
@@ -17435,7 +16863,6 @@
           <t>van RYSSELBERGHE</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
           <t>belge</t>
@@ -17463,7 +16890,6 @@
           <t>SAINT-GAUDENS</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -17491,7 +16917,6 @@
           <t>SALY</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
           <t>française</t>
@@ -17519,7 +16944,6 @@
           <t>SALZILLO</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -17547,7 +16971,6 @@
           <t>SÁNCHEZ COELLO</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -17575,7 +16998,6 @@
           <t>da SANGALLO</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17603,7 +17025,6 @@
           <t>SANMARTINO</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr">
         <is>
           <t>Italienne</t>
@@ -17631,7 +17052,6 @@
           <t>SANSOVINO</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17659,7 +17079,6 @@
           <t>SANSOVINO</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17719,7 +17138,6 @@
           <t>SARGENT</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -17747,7 +17165,6 @@
           <t>SARRAZIN</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr">
         <is>
           <t>française</t>
@@ -17775,7 +17192,6 @@
           <t>del SARTO</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17803,7 +17219,6 @@
           <t>SCHADOW</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -17831,7 +17246,6 @@
           <t>SCHIAFFINO</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17859,7 +17273,6 @@
           <t>SCHIELE</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr">
         <is>
           <t>autrichienne</t>
@@ -17887,7 +17300,6 @@
           <t>SCHLÜTER</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
         <is>
           <t>Allemande</t>
@@ -17915,7 +17327,6 @@
           <t>SERPOTTA</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -17943,7 +17354,6 @@
           <t>SERRA</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -17971,7 +17381,6 @@
           <t>SÉRUSIER</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
           <t>française</t>
@@ -17999,7 +17408,6 @@
           <t>da SETTIGNANO</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -18027,7 +17435,6 @@
           <t>SEURAT</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
           <t>française</t>
@@ -18055,7 +17462,6 @@
           <t>SICKERT</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -18083,7 +17489,6 @@
           <t>SIEMERING</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -18111,7 +17516,6 @@
           <t>SIGNAC</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
           <t>française</t>
@@ -18139,7 +17543,6 @@
           <t>SIGNORELLI</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -18167,7 +17570,6 @@
           <t>de SILOÉ</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -18195,7 +17597,6 @@
           <t>de SILOÉ</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -18223,7 +17624,6 @@
           <t>SINDING</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr">
         <is>
           <t>norvégienne</t>
@@ -18251,7 +17651,6 @@
           <t>SISLEY</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr">
         <is>
           <t>française</t>
@@ -18279,7 +17678,6 @@
           <t>SLEVOGT</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -18339,7 +17737,6 @@
           <t>SLUTER</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -18367,7 +17764,6 @@
           <t>SNYDERS</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
           <t>belge</t>
@@ -18395,7 +17791,6 @@
           <t>SOUTINE</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
           <t>biélorusse</t>
@@ -18423,7 +17818,6 @@
           <t>de STAËL</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
           <t>russe</t>
@@ -18451,7 +17845,6 @@
           <t>STEEN</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -18479,7 +17872,6 @@
           <t>STEVENS</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -18507,7 +17899,6 @@
           <t>STONE</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -18535,7 +17926,6 @@
           <t>STORY</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -18563,7 +17953,6 @@
           <t>STOSS</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -18591,7 +17980,6 @@
           <t>STOUF</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
           <t>française</t>
@@ -18619,7 +18007,6 @@
           <t>STRAUB</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -18647,7 +18034,6 @@
           <t>STROZZI</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -18675,7 +18061,6 @@
           <t>STUART</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -18703,7 +18088,6 @@
           <t>STUBBS</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -18731,7 +18115,6 @@
           <t>LE SUEUR</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
           <t>française</t>
@@ -18759,7 +18142,6 @@
           <t>LE SUEUR</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
           <t>française</t>
@@ -18787,7 +18169,6 @@
           <t>TAFT</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -18815,7 +18196,6 @@
           <t>TAGLIOLINI</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
           <t>Italienne</t>
@@ -18843,7 +18223,6 @@
           <t>TAKAMURA</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
           <t>japonaise</t>
@@ -18871,7 +18250,6 @@
           <t>TANGUY</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
           <t>française</t>
@@ -18899,7 +18277,6 @@
           <t>TASSAERT</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
           <t>Flamande</t>
@@ -18927,7 +18304,6 @@
           <t>TENIERS LE JEUNE</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr"/>
       <c r="D657" t="inlineStr">
         <is>
           <t>belge</t>
@@ -18955,7 +18331,6 @@
           <t>van TETRODE</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -18983,7 +18358,6 @@
           <t>THORNYCROFT</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -19011,7 +18385,6 @@
           <t>THORVALDSEN</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
           <t>danoise</t>
@@ -19039,7 +18412,6 @@
           <t>TIBALDI</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19067,7 +18439,6 @@
           <t>TIEPOLO</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19095,7 +18466,6 @@
           <t>TIETZ</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -19123,7 +18493,6 @@
           <t>TISSOT</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
           <t>française</t>
@@ -19151,7 +18520,6 @@
           <t>TORRETTI</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19179,7 +18547,6 @@
           <t>TORRIGIANO</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19207,7 +18574,6 @@
           <t>de TOULOUSE-LAUTREC</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
           <t>française</t>
@@ -19235,7 +18601,6 @@
           <t>de la TOUR</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr">
         <is>
           <t>française</t>
@@ -19263,7 +18628,6 @@
           <t>de la TOUR</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
           <t>française</t>
@@ -19291,7 +18655,6 @@
           <t>TRIBOLO</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19319,7 +18682,6 @@
           <t>TROUBETZKOY</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
           <t>russe</t>
@@ -19347,7 +18709,6 @@
           <t>TUBY</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr">
         <is>
           <t>française</t>
@@ -19375,7 +18736,6 @@
           <t>TURA</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19403,7 +18763,6 @@
           <t>TURNER</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -19431,7 +18790,6 @@
           <t>UCCELLO</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19459,7 +18817,6 @@
           <t>UTRILLO</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
           <t>française</t>
@@ -19487,7 +18844,6 @@
           <t>VALADON</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr">
         <is>
           <t>française</t>
@@ -19515,7 +18871,6 @@
           <t>della VALLE</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19543,7 +18898,6 @@
           <t>VALLOTTON</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -19571,7 +18925,6 @@
           <t>VALTAT</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
           <t>française</t>
@@ -19631,7 +18984,6 @@
           <t>VELA</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
           <t>suisse</t>
@@ -19659,7 +19011,6 @@
           <t>VELÁZQUEZ</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -19687,7 +19038,6 @@
           <t>van de VELDE LE JEUNE</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -19715,7 +19065,6 @@
           <t>VENEZIANO</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19743,7 +19092,6 @@
           <t>VENEZIANO</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19771,7 +19119,6 @@
           <t>VENTURA</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19799,7 +19146,6 @@
           <t>VERHULST</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
           <t>belge</t>
@@ -19827,7 +19173,6 @@
           <t>VERMEER</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -19855,7 +19200,6 @@
           <t>VERNET</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
           <t>française</t>
@@ -19883,7 +19227,6 @@
           <t>VÉRONÈSE</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19911,7 +19254,6 @@
           <t>del VERROCCHIO</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -19939,7 +19281,6 @@
           <t>VIGÉE LE BRUN</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr"/>
       <c r="D693" t="inlineStr">
         <is>
           <t>française</t>
@@ -19967,7 +19308,6 @@
           <t>VILAR</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -19995,7 +19335,6 @@
           <t>de VINCI</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr"/>
       <c r="D695" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20023,7 +19362,6 @@
           <t>da VINCI</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr"/>
       <c r="D696" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20051,7 +19389,6 @@
           <t>VISCHER L'ANCIEN</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -20079,7 +19416,6 @@
           <t>VITTORIA</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20107,7 +19443,6 @@
           <t>VIVARINI</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20135,7 +19470,6 @@
           <t>VIVARINI</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20163,7 +19497,6 @@
           <t>VIVARINI</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr"/>
       <c r="D701" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20191,7 +19524,6 @@
           <t>da VOLTERRA</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr"/>
       <c r="D702" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20219,7 +19551,6 @@
           <t>VOUET</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr">
         <is>
           <t>française</t>
@@ -20247,7 +19578,6 @@
           <t>de VRIES</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr"/>
       <c r="D704" t="inlineStr">
         <is>
           <t>néerlandaise</t>
@@ -20275,7 +19605,6 @@
           <t>VROUBEL</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr">
         <is>
           <t>russe</t>
@@ -20303,7 +19632,6 @@
           <t>VUILLARD</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr"/>
       <c r="D706" t="inlineStr">
         <is>
           <t>française</t>
@@ -20331,7 +19659,6 @@
           <t>WANG</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -20359,7 +19686,6 @@
           <t>WARIN</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr"/>
       <c r="D708" t="inlineStr">
         <is>
           <t>française</t>
@@ -20387,7 +19713,6 @@
           <t>WATERHOUSE</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr"/>
       <c r="D709" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -20415,7 +19740,6 @@
           <t>WATTEAU</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
           <t>française</t>
@@ -20443,7 +19767,6 @@
           <t>von WEREFKIN</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr">
         <is>
           <t>russe</t>
@@ -20471,7 +19794,6 @@
           <t>WEST</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -20499,7 +19821,6 @@
           <t>WHISTLER</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -20527,7 +19848,6 @@
           <t>WHITNEY</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -20555,7 +19875,6 @@
           <t>WILDT</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20583,7 +19902,6 @@
           <t>WILSON</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -20611,7 +19929,6 @@
           <t>WITZ</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -20639,7 +19956,6 @@
           <t>WOOD</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -20667,7 +19983,6 @@
           <t>WOOD</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
           <t>américaine</t>
@@ -20695,7 +20010,6 @@
           <t>WRIGHT of DERBY</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
@@ -20723,7 +20037,6 @@
           <t>WU</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -20751,7 +20064,6 @@
           <t>YUAN</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -20811,7 +20123,6 @@
           <t>da ZEVIO</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr">
         <is>
           <t>italienne</t>
@@ -20839,7 +20150,6 @@
           <t>ZHAO</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr">
         <is>
           <t>chinoise</t>
@@ -20889,10 +20199,14 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" t="inlineStr"/>
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>ZHU da</t>
+          <t>ZHU</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -20927,7 +20241,6 @@
           <t>ZOFFANY</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
           <t>allemande</t>
@@ -20955,7 +20268,6 @@
           <t>de ZURBARÁN</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
           <t>espagnole</t>
@@ -20983,7 +20295,6 @@
           <t>ZÜRN</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
           <t>allemande</t>
